--- a/nriss-patch-2/ig/ValueSet-fr-vs-allergy-code.xlsx
+++ b/nriss-patch-2/ig/ValueSet-fr-vs-allergy-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T09:15:45+00:00</t>
+    <t>2026-10-01T07:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -129,7 +129,7 @@
     <t>ValueSet URL</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-allergie-vaccin-cisis|20260619134043</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-allergie-vaccin-cisis|20260916095456</t>
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/terminologie-sms</t>
